--- a/events/Tacen_2019_WC/Tacen_2019_WC_start.xlsx
+++ b/events/Tacen_2019_WC/Tacen_2019_WC_start.xlsx
@@ -29112,11 +29112,6 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
-        <is>
-          <t>71799</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -29732,11 +29727,6 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
-        <is>
-          <t>39079</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -30624,11 +30614,6 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
-        <is>
-          <t>39079</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -31541,11 +31526,6 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
-        <is>
-          <t>39079</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -31602,11 +31582,6 @@
       <c r="R530" t="inlineStr">
         <is>
           <t>BOYD Trevor</t>
-        </is>
-      </c>
-      <c r="U530" t="inlineStr">
-        <is>
-          <t>71799</t>
         </is>
       </c>
     </row>
